--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2024/NEW_HAMPSHIRE_2024.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2024/NEW_HAMPSHIRE_2024.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,9 +395,14 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C3">
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Mitontic</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Oxchuc</t>
@@ -465,9 +485,14 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>San Cristóbal de las Casas</t>
+          <t>San Cristóbal De Las Casas</t>
         </is>
       </c>
       <c r="C8">
@@ -478,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Siltepec</t>
@@ -491,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -504,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Tapalapa</t>
@@ -517,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Teopisca</t>
@@ -530,9 +575,14 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C13">
@@ -545,7 +595,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -561,9 +611,14 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C15">
@@ -592,9 +647,14 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C17">
@@ -623,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -636,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -649,9 +719,14 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C21">
@@ -664,7 +739,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -680,9 +755,14 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C23">
@@ -711,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -724,9 +809,14 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C26">
@@ -744,7 +834,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C27">
@@ -755,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Cualác</t>
@@ -768,9 +863,14 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Huitzuco de los Figueroa</t>
+          <t>Huitzuco De Los Figueroa</t>
         </is>
       </c>
       <c r="C29">
@@ -781,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Igualapa</t>
@@ -794,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Malinaltepec</t>
@@ -807,9 +917,14 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mártir de Cuilapan</t>
+          <t>Mártir De Cuilapan</t>
         </is>
       </c>
       <c r="C32">
@@ -820,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Ometepec</t>
@@ -833,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -846,9 +971,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Taxco de Alarcón</t>
+          <t>Taxco De Alarcón</t>
         </is>
       </c>
       <c r="C35">
@@ -859,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Tlacoapa</t>
@@ -872,9 +1007,14 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C37">
@@ -903,9 +1043,14 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C39">
@@ -916,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>San Bartolo Tutotepec</t>
@@ -929,9 +1079,14 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C41">
@@ -960,9 +1115,14 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Autlán de Navarro</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C43">
@@ -973,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Casimiro Castillo</t>
@@ -986,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Cuquío</t>
@@ -999,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Degollado</t>
@@ -1012,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Puerto Vallarta</t>
@@ -1025,9 +1205,14 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C48">
@@ -1040,7 +1225,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Michoacán de Ocampo</t>
+          <t>Michoacán De Ocampo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1056,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Maravatío</t>
@@ -1069,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -1082,9 +1277,14 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C52">
@@ -1113,9 +1313,14 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C54">
@@ -1144,9 +1349,14 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C56">
@@ -1164,7 +1374,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Ejutla de Crespo</t>
+          <t>Heroica Ciudad De Ejutla De Crespo</t>
         </is>
       </c>
       <c r="C57">
@@ -1175,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Santa Cruz Zenzontepec</t>
@@ -1188,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Santa María Temaxcaltepec</t>
@@ -1201,9 +1421,14 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C60">
@@ -1232,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -1245,9 +1475,14 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C63">
@@ -1258,9 +1493,14 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Palmar de Bravo</t>
+          <t>Palmar De Bravo</t>
         </is>
       </c>
       <c r="C64">
@@ -1271,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Santo Tomás Hueyotlipan</t>
@@ -1284,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Tlapanalá</t>
@@ -1297,9 +1547,14 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C67">
@@ -1328,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>El Marqués</t>
@@ -1341,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -1354,9 +1619,14 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C71">
@@ -1385,9 +1655,14 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C73">
@@ -1416,9 +1691,14 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C75">
@@ -1431,7 +1711,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Veracruz de Ignacio de la Llave</t>
+          <t>Veracruz De Ignacio De La Llave</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1447,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Uxpanapa</t>
@@ -1460,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -1473,9 +1763,14 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C79">
@@ -1504,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Fresnillo</t>
@@ -1517,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Sombrerete</t>
@@ -1530,9 +1835,14 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Villa de Cos</t>
+          <t>Villa De Cos</t>
         </is>
       </c>
       <c r="C83">
@@ -1543,9 +1853,14 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C84">
@@ -1558,7 +1873,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C85">
@@ -1566,41 +1881,6 @@
       </c>
       <c r="D85">
         <v>1</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 808,027</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de Mexicanas y Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Junio de 2025</t>
-        </is>
       </c>
     </row>
   </sheetData>
